--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,47 +597,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,39 +684,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -823,9 +827,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -888,17 +892,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1040,24 +1044,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,8 +1116,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1122,37 +1128,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1186,11 +1194,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1261,9 +1269,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1326,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1413,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1478,7 +1486,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1487,15 +1495,15 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1623,51 +1631,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1701,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1735,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1774,7 +1778,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1808,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1847,7 +1851,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1881,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1914,17 +1918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1947,19 +1951,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1987,19 +1991,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2020,19 +2024,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2057,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2065,8 +2069,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>17</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2075,37 +2081,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2139,7 +2147,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2148,15 +2156,15 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2166,19 +2174,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2206,9 +2214,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -2239,19 +2247,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2284,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2284,10 +2292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2296,39 +2302,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,20 +2357,20 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2375,11 +2379,11 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2426,59 +2430,55 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2521,15 +2521,15 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2584,10 +2584,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2596,39 +2594,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2653,18 +2649,16 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2673,39 +2667,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2738,8 +2730,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2748,37 +2742,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2803,7 +2799,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2825,11 +2821,11 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2846,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2876,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2884,47 +2880,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2952,17 +2952,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2992,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3030,8 +3030,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>1</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3040,37 +3042,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3103,8 +3107,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>17</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3113,37 +3119,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3168,7 +3176,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3176,10 +3184,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3188,39 +3194,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3256,9 +3260,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3288,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3318,7 +3322,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3326,51 +3330,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3476,10 +3476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3488,39 +3486,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3545,7 +3541,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3553,10 +3549,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3565,39 +3559,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3669,12 +3661,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3699,7 +3691,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3707,51 +3699,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3776,7 +3764,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3784,8 +3772,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3794,37 +3784,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3858,7 +3850,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3892,12 +3884,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3922,7 +3914,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3930,47 +3922,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3995,55 +3991,59 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4076,47 +4076,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4141,16 +4145,18 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4159,37 +4165,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4223,11 +4231,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4257,12 +4265,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4287,7 +4295,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4309,11 +4317,11 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4330,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4369,11 +4377,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4403,12 +4411,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4436,17 +4444,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4476,12 +4484,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4506,7 +4514,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4514,51 +4522,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4583,16 +4587,16 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4601,15 +4605,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4630,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4665,11 +4669,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4699,12 +4703,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4729,12 +4733,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
@@ -4751,11 +4755,11 @@
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4772,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4811,11 +4815,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4845,12 +4849,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4875,20 +4879,20 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4897,11 +4901,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4918,12 +4922,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4948,7 +4952,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4956,8 +4960,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4966,37 +4972,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5021,33 +5029,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5064,12 +5072,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5094,7 +5102,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5102,10 +5110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5114,39 +5120,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5171,33 +5175,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5214,12 +5218,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5244,7 +5248,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5252,51 +5256,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5321,33 +5321,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5402,10 +5402,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5414,39 +5412,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5474,22 +5470,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5497,7 +5493,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,12 +5510,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5591,12 +5587,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5621,33 +5617,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5741,12 +5737,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5771,33 +5767,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 101,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 67,3%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5814,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5891,12 +5887,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5921,33 +5917,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,12 +5960,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6041,12 +6037,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6071,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>24</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6114,82 +6110,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,39 +607,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -827,9 +823,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -889,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,39 +905,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1046,9 +1046,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,10 +1116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1128,41 +1126,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1194,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1258,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,8 +1262,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1276,39 +1274,41 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1334,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1415,9 +1415,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1477,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2069,10 +2069,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2081,41 +2079,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2147,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2211,7 +2207,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2219,8 +2215,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2229,39 +2227,41 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2360,17 +2360,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2393,21 +2393,21 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2433,17 +2433,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2466,21 +2466,21 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2503,33 +2503,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,14 +2546,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2576,33 +2576,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2619,14 +2619,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2649,16 +2649,16 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2667,15 +2667,15 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,14 +2692,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2730,10 +2730,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2742,41 +2740,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2799,12 +2795,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2821,11 +2817,11 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2919,14 +2915,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2949,7 +2945,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2971,11 +2967,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2992,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,14 +3065,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3107,10 +3103,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3119,41 +3113,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3176,7 +3168,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3184,8 +3176,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3194,39 +3188,41 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3249,7 +3245,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3257,8 +3253,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3267,39 +3265,41 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3333,9 +3333,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3365,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3398,17 +3398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3477,11 +3477,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3511,14 +3511,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3541,33 +3541,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3622,10 +3622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3634,41 +3632,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3691,7 +3687,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3700,24 +3696,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3734,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3811,14 +3807,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3850,11 +3846,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3884,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3961,14 +3957,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3991,7 +3987,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3999,10 +3995,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4011,39 +4005,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4115,12 +4107,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4192,14 +4184,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4222,7 +4214,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4230,8 +4222,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4240,39 +4234,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4295,7 +4291,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4303,8 +4299,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4313,39 +4311,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4379,9 +4379,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4411,14 +4411,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4444,17 +4444,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4484,14 +4484,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4523,11 +4523,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4557,14 +4557,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4587,33 +4587,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,14 +4630,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4669,11 +4669,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4703,14 +4703,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4733,16 +4733,16 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4751,15 +4751,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4776,14 +4776,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4815,11 +4815,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4849,14 +4849,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4901,11 +4901,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4922,14 +4922,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4960,10 +4960,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4972,39 +4970,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5072,14 +5068,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5102,7 +5098,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5110,8 +5106,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5120,39 +5118,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5178,9 +5178,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -5218,14 +5218,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5259,9 +5259,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5291,14 +5291,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5321,20 +5321,20 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,14 +5364,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5403,11 +5403,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,14 +5437,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5467,33 +5467,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5510,14 +5510,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5548,10 +5548,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5560,41 +5558,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5617,33 +5613,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5660,12 +5656,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5737,14 +5733,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5767,33 +5763,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5806,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5887,14 +5883,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5917,33 +5913,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5960,12 +5956,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6037,14 +6033,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6067,33 +6063,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,12 +6106,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6187,14 +6183,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6217,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6260,12 +6256,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6337,14 +6333,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6367,33 +6363,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6410,12 +6406,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6487,14 +6483,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6517,33 +6513,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6560,82 +6556,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>15</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,37 +609,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +677,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -855,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,59 +885,55 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -973,9 +969,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,7 +1031,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1044,7 +1040,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1053,15 +1049,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1117,7 +1113,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1151,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,7 +1177,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1189,47 +1185,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,10 +1262,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1274,39 +1272,37 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1339,8 +1335,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1349,37 +1347,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1415,9 +1415,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,8 +1704,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1714,37 +1716,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1778,11 +1782,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1853,9 +1857,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1918,17 +1922,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1997,11 +2001,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2035,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2070,7 +2074,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2079,15 +2083,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2143,11 +2147,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2215,51 +2219,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2400,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2473,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2579,19 +2579,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2612,19 +2612,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2657,8 +2657,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>17</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2667,37 +2669,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2731,7 +2735,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2740,15 +2744,15 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2758,19 +2762,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2798,9 +2802,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2831,19 +2835,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2868,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2876,10 +2880,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2888,39 +2890,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2945,20 +2945,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3018,59 +3018,55 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3095,7 +3091,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3104,7 +3100,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3113,15 +3109,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3138,12 +3134,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3168,7 +3164,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3176,10 +3172,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3188,39 +3182,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3245,18 +3237,16 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3265,39 +3255,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3322,7 +3310,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3330,8 +3318,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3340,37 +3330,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3395,7 +3387,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3417,11 +3409,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3438,12 +3430,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3468,7 +3460,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3476,47 +3468,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3544,17 +3540,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3584,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3614,7 +3610,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3622,8 +3618,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3632,37 +3630,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3695,8 +3695,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>17</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3705,37 +3707,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3760,7 +3764,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3768,10 +3772,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3780,39 +3782,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3848,9 +3848,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3918,51 +3918,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3990,17 +3986,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4030,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4060,7 +4056,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4068,10 +4064,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4080,39 +4074,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4137,7 +4129,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4145,10 +4137,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4157,39 +4147,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,12 +4249,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4291,7 +4279,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4299,51 +4287,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4368,7 +4352,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4376,8 +4360,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4386,37 +4372,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4450,7 +4438,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4484,12 +4472,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4514,7 +4502,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4522,47 +4510,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4587,55 +4579,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4660,7 +4656,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4668,47 +4664,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4733,16 +4733,18 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>21</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4751,37 +4753,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4815,11 +4819,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4849,12 +4853,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4879,7 +4883,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4901,11 +4905,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4922,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4961,11 +4965,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4995,12 +4999,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5028,17 +5032,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5068,12 +5072,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5098,7 +5102,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5106,51 +5110,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5175,16 +5175,16 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5193,15 +5193,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5257,11 +5257,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5403,11 +5403,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5467,20 +5467,20 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5548,8 +5548,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5558,37 +5560,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5613,33 +5617,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5656,12 +5660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5686,7 +5690,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5694,10 +5698,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5706,39 +5708,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5763,33 +5763,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5844,51 +5844,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5913,33 +5909,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5956,12 +5952,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5986,7 +5982,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5994,10 +5990,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6006,39 +6000,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6066,22 +6058,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6089,7 +6081,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6106,12 +6098,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6183,12 +6175,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6213,33 +6205,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,12 +6248,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6333,12 +6325,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6363,33 +6355,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 101,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 67,3%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6406,12 +6398,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6483,12 +6475,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6513,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6556,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6633,12 +6625,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6663,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>24</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6706,82 +6698,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,39 +607,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -821,7 +825,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,20 +889,20 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -907,11 +911,11 @@
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1001,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1039,8 +1043,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>15</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1049,37 +1055,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1115,9 +1123,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1147,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1185,10 +1193,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1197,39 +1203,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1263,7 +1267,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1297,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,59 +1331,55 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1415,9 +1415,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1495,15 +1495,15 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1593,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1631,47 +1631,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,10 +1708,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1716,39 +1718,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1781,8 +1781,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1791,37 +1793,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1857,9 +1861,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1889,12 +1893,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1922,17 +1926,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,12 +1966,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2001,11 +2005,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2035,12 +2039,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2074,24 +2078,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2108,12 +2112,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2138,7 +2142,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2146,8 +2150,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2156,37 +2162,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2220,11 +2228,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,12 +2262,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2295,9 +2303,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,12 +2335,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2360,17 +2368,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,12 +2408,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2439,11 +2447,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,12 +2481,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2503,7 +2511,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2512,7 +2520,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2521,15 +2529,15 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,12 +2554,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2585,11 +2593,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2619,12 +2627,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,7 +2657,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2657,51 +2665,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2735,11 +2739,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,12 +2773,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2808,7 +2812,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2842,12 +2846,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2881,7 +2885,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2915,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2948,17 +2952,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2981,19 +2985,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3021,19 +3025,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3054,19 +3058,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3091,7 +3095,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3099,8 +3103,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>17</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3109,37 +3115,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3164,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3173,7 +3181,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3182,15 +3190,15 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3200,19 +3208,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3240,9 +3248,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3273,19 +3281,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3310,7 +3318,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3318,10 +3326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3330,39 +3336,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3387,20 +3391,20 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3409,11 +3413,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3430,12 +3434,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3460,59 +3464,55 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3555,15 +3555,15 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3618,10 +3618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3630,39 +3628,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3687,18 +3683,16 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3707,39 +3701,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3764,7 +3756,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3772,8 +3764,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3782,37 +3776,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3837,7 +3833,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3859,11 +3855,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3880,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3910,7 +3906,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3918,47 +3914,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3986,17 +3986,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4064,8 +4064,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4074,37 +4076,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4129,7 +4133,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4137,8 +4141,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>17</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4147,37 +4153,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4202,7 +4210,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4210,10 +4218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4222,39 +4228,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4290,9 +4294,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4322,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4352,7 +4356,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4360,51 +4364,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4432,17 +4432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4472,12 +4472,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4510,10 +4510,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4522,39 +4520,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4579,7 +4575,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4587,10 +4583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4599,39 +4593,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4695,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4733,7 +4725,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4741,51 +4733,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4810,7 +4798,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4818,8 +4806,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4828,37 +4818,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4892,7 +4884,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4926,12 +4918,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4956,7 +4948,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4964,47 +4956,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5029,55 +5025,59 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5110,47 +5110,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5175,16 +5179,18 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>21</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5193,37 +5199,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5257,11 +5265,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5291,12 +5299,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5321,7 +5329,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5343,11 +5351,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5372,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5403,11 +5411,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,12 +5445,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5470,17 +5478,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5510,12 +5518,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5540,7 +5548,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5548,51 +5556,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5617,16 +5621,16 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5635,15 +5639,15 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5660,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5699,11 +5703,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5721,7 +5725,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5733,12 +5737,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5763,12 +5767,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
@@ -5785,11 +5789,11 @@
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5806,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5845,11 +5849,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5879,12 +5883,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5909,20 +5913,20 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5931,11 +5935,11 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5952,12 +5956,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5982,7 +5986,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5990,8 +5994,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6000,37 +6006,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6055,33 +6063,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6098,12 +6106,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6128,7 +6136,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6136,10 +6144,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6148,39 +6154,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6205,33 +6209,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6248,12 +6252,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6278,7 +6282,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6286,51 +6290,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6355,33 +6355,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6436,10 +6436,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6448,39 +6446,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6508,22 +6504,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6531,7 +6527,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6544,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6625,12 +6621,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6655,33 +6651,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,12 +6694,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6775,12 +6771,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6805,33 +6801,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 101,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 67,3%</t>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>28</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6848,12 +6844,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6925,12 +6921,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6955,33 +6951,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +6994,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7075,12 +7071,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7105,33 +7101,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>24</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7148,82 +7144,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,15 +607,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -739,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -759,41 +753,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -816,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -824,8 +816,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -834,39 +828,41 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -889,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,37 +905,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1043,10 +1043,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1055,41 +1053,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1123,9 +1119,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1155,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,8 +1189,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1203,39 +1201,41 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1267,11 +1267,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1331,20 +1331,20 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1477,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1631,10 +1631,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1643,39 +1641,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1743,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1820,14 +1816,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1861,9 +1857,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1893,14 +1889,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1923,7 +1919,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1931,8 +1927,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1941,39 +1939,41 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2005,11 +2005,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2039,14 +2039,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2080,9 +2080,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2112,14 +2112,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2150,10 +2150,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2162,41 +2160,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2228,11 +2224,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2262,14 +2258,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2300,8 +2296,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2310,39 +2308,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2368,17 +2368,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2408,14 +2408,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2449,9 +2449,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2511,33 +2511,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2554,14 +2554,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2593,11 +2593,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2627,14 +2627,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2666,24 +2666,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,14 +2700,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2739,11 +2739,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2773,14 +2773,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2812,11 +2812,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2846,14 +2846,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2885,11 +2885,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2919,14 +2919,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2992,14 +2992,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3031,11 +3031,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3065,14 +3065,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3103,10 +3103,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3115,41 +3113,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3181,11 +3177,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3215,14 +3211,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3253,8 +3249,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3263,39 +3261,41 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3361,14 +3361,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3394,17 +3394,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3427,21 +3427,21 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3467,17 +3467,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3500,21 +3500,21 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3537,33 +3537,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3580,14 +3580,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3610,33 +3610,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3653,14 +3653,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3683,16 +3683,16 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3701,15 +3701,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,14 +3726,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3764,10 +3764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3776,41 +3774,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3833,12 +3829,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3855,11 +3851,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3876,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,14 +3949,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3983,7 +3979,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4005,11 +4001,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4026,12 +4022,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4103,14 +4099,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4133,7 +4129,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4141,10 +4137,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4153,41 +4147,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4210,7 +4202,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4218,8 +4210,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4228,39 +4222,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4283,7 +4279,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4291,8 +4287,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4301,39 +4299,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4367,9 +4367,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4399,14 +4399,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4432,17 +4432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4472,14 +4472,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4511,11 +4511,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4545,14 +4545,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4575,33 +4575,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4618,14 +4618,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4656,10 +4656,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4668,41 +4666,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4725,7 +4721,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4734,24 +4730,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4768,12 +4764,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4845,14 +4841,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4884,11 +4880,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4918,12 +4914,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4995,14 +4991,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5025,7 +5021,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5033,10 +5029,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5045,39 +5039,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5149,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5226,14 +5218,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5264,8 +5256,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5274,39 +5268,41 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5329,7 +5325,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5337,8 +5333,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5347,39 +5345,41 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5413,9 +5413,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5445,14 +5445,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5478,17 +5478,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5518,14 +5518,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5557,11 +5557,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5591,14 +5591,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5621,33 +5621,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,14 +5664,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5703,11 +5703,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5737,14 +5737,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5767,16 +5767,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5785,15 +5785,15 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,14 +5810,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5849,11 +5849,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5883,14 +5883,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5935,11 +5935,11 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5956,14 +5956,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5994,10 +5994,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6006,39 +6004,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6106,14 +6102,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6136,7 +6132,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6144,8 +6140,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6154,39 +6152,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6212,9 +6212,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -6252,14 +6252,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6293,9 +6293,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6325,14 +6325,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6355,20 +6355,20 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6377,11 +6377,11 @@
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6398,14 +6398,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6437,11 +6437,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6471,14 +6471,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6501,33 +6501,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6544,14 +6544,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6582,10 +6582,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6594,41 +6592,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6651,33 +6647,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,12 +6690,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6771,14 +6767,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6801,33 +6797,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6844,12 +6840,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6921,14 +6917,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6951,33 +6947,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6994,12 +6990,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7071,14 +7067,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7101,33 +7097,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7144,12 +7140,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7221,14 +7217,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7251,33 +7247,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7294,12 +7290,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7371,14 +7367,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7401,33 +7397,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7444,12 +7440,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7521,14 +7517,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7551,33 +7547,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7594,82 +7590,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,15 +607,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,10 +889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -905,39 +899,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -971,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1005,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1057,11 +1049,11 @@
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1108,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,37 +1120,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1228,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1269,9 +1265,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1374,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1413,7 +1409,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1447,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,55 +1473,59 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1561,9 +1561,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1739,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,59 +1769,55 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1889,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1919,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1927,10 +1923,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1939,39 +1933,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2007,9 +1999,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2039,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2069,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2077,8 +2069,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2087,37 +2081,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2151,7 +2147,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2185,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2215,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2223,47 +2219,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2296,51 +2296,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2374,7 +2370,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2408,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2447,7 +2443,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2481,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2514,9 +2510,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2554,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2584,7 +2580,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2592,47 +2588,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2675,15 +2675,15 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2773,12 +2773,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2806,9 +2806,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2846,12 +2846,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2958,24 +2958,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2992,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3065,12 +3065,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3106,9 +3106,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3249,10 +3249,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3261,39 +3259,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3361,12 +3357,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3434,12 +3430,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3475,9 +3471,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3507,12 +3503,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3537,55 +3533,59 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3613,17 +3613,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3701,15 +3701,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3719,19 +3719,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3774,15 +3774,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3792,19 +3792,19 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3840,9 +3840,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3902,59 +3902,55 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3988,7 +3984,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3997,7 +3993,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4005,7 +4001,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4022,12 +4018,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4052,7 +4048,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4060,10 +4056,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4072,39 +4066,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4132,9 +4124,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -4172,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4249,12 +4241,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4279,7 +4271,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4287,10 +4279,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4299,39 +4289,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4364,8 +4352,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4374,37 +4364,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4472,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4502,7 +4494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4510,47 +4502,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4575,55 +4571,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4691,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4739,15 +4739,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4802,51 +4802,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4874,9 +4870,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -4914,12 +4910,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4944,7 +4940,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4952,10 +4948,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4964,39 +4958,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5021,7 +5013,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5030,24 +5022,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5064,12 +5056,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5141,12 +5133,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5171,7 +5163,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5179,51 +5171,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5295,12 +5283,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5325,7 +5313,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5333,10 +5321,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5345,39 +5331,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5402,7 +5386,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5410,8 +5394,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5420,37 +5406,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5475,7 +5463,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5483,8 +5471,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5493,37 +5483,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5548,7 +5540,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5556,47 +5548,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5621,55 +5617,59 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5703,11 +5703,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5767,16 +5767,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5785,15 +5785,15 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5849,11 +5849,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5913,20 +5913,20 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5935,11 +5935,11 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5997,9 +5997,9 @@
       <c r="I75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6059,16 +6059,16 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6077,15 +6077,15 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6140,51 +6140,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6209,7 +6205,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6231,11 +6227,11 @@
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6252,12 +6248,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6291,7 +6287,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6313,7 +6309,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6325,12 +6321,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6358,9 +6354,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
@@ -6398,12 +6394,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6428,7 +6424,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6436,47 +6432,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6523,11 +6523,11 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6647,33 +6647,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6728,51 +6728,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6797,25 +6793,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,3%</t>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6823,7 +6819,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6840,12 +6836,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6870,7 +6866,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6878,10 +6874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6890,39 +6884,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6947,33 +6939,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6990,12 +6982,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7067,12 +7059,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7097,33 +7089,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,7%</t>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>26</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7140,12 +7132,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7217,12 +7209,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7250,22 +7242,22 @@
           <t>R$ 101,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,2%</t>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7273,7 +7265,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7290,12 +7282,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7367,12 +7359,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7397,33 +7389,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7440,12 +7432,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7517,12 +7509,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7550,22 +7542,22 @@
           <t>R$ 101,00</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7573,7 +7565,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7590,12 +7582,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7667,12 +7659,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7697,33 +7689,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7740,82 +7732,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -771,19 +775,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +820,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -892,22 +900,22 @@
       <c r="I6" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -917,19 +925,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,7 +1048,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1063,19 +1075,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1147,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1185,10 +1197,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1197,39 +1207,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,8 +1270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1272,37 +1282,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1338,9 +1350,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1349,11 +1361,11 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,8 +1420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1418,37 +1432,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,59 +1489,55 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,47 +1570,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1632,7 +1648,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1641,7 +1657,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1649,7 +1665,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,8 +1720,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1714,37 +1732,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1772,15 +1792,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1812,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,8 +1870,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1860,37 +1882,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,7 +1939,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,24 +1948,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +2012,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,8 +2020,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2006,37 +2032,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,7 +2089,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2069,10 +2097,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2081,39 +2107,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2181,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2258,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2299,9 +2323,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2331,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2404,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2443,11 +2467,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2477,12 +2501,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2510,15 +2534,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2550,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2580,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2588,51 +2612,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2657,7 +2677,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2666,24 +2686,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2739,7 +2759,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2773,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2806,17 +2826,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2846,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2884,47 +2904,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2949,7 +2973,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2957,8 +2981,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>8</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2967,37 +2993,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3031,7 +3059,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3065,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3095,7 +3123,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3106,9 +3134,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3117,11 +3145,11 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3138,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3179,9 +3207,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3211,12 +3239,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3241,7 +3269,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3249,8 +3277,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3259,37 +3289,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3323,11 +3355,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3357,12 +3389,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3387,7 +3419,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3409,11 +3441,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3430,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3469,11 +3501,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3503,12 +3535,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3533,59 +3565,55 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3619,7 +3647,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3653,12 +3681,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3683,7 +3711,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3692,7 +3720,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3701,15 +3729,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3754,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3799,12 +3827,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3829,55 +3857,59 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3905,17 +3937,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3938,19 +3970,19 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3975,7 +4007,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3983,8 +4015,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>17</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3993,37 +4027,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4048,7 +4084,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4057,24 +4093,24 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4084,19 +4120,19 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4124,9 +4160,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -4157,19 +4193,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4194,7 +4230,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4202,10 +4238,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4214,39 +4248,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4271,7 +4303,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4282,9 +4314,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4293,11 +4325,11 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4307,19 +4339,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,12 +4423,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4430,7 +4462,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4457,19 +4489,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4494,7 +4526,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4502,10 +4534,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4514,39 +4544,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4571,59 +4599,55 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4659,9 +4683,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4684,19 +4708,19 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4721,7 +4745,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4730,7 +4754,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4739,15 +4763,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4757,19 +4781,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4803,11 +4827,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4830,19 +4854,19 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4870,19 +4894,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4903,19 +4927,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4949,11 +4973,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4976,19 +5000,19 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5013,7 +5037,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5022,7 +5046,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5031,15 +5055,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5049,19 +5073,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5086,7 +5110,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5094,10 +5118,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5106,39 +5128,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5174,9 +5194,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5199,19 +5219,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5236,7 +5256,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5244,51 +5264,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5313,7 +5329,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5321,8 +5337,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5331,37 +5349,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5386,7 +5406,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5394,10 +5414,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5406,39 +5424,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5463,7 +5479,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5471,10 +5487,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5483,39 +5497,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5540,7 +5552,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5548,10 +5560,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5560,39 +5570,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5617,59 +5625,55 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5697,17 +5701,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5737,12 +5741,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5767,7 +5771,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5776,7 +5780,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5785,15 +5789,15 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5840,7 +5844,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5849,24 +5853,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5883,12 +5887,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5916,7 +5920,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5924,9 +5928,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5956,12 +5960,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5986,7 +5990,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5994,47 +5998,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6059,16 +6067,16 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6077,15 +6085,15 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6102,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6132,7 +6140,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6140,47 +6148,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6205,7 +6217,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6227,11 +6239,11 @@
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6248,12 +6260,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6278,7 +6290,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6286,8 +6298,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6296,37 +6310,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6351,7 +6367,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6359,8 +6375,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6369,37 +6387,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6424,7 +6444,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6432,10 +6452,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6444,39 +6462,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6544,12 +6560,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6585,9 +6601,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6605,7 +6621,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6617,12 +6633,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6650,7 +6666,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6658,9 +6674,9 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6690,12 +6706,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6729,11 +6745,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6763,12 +6779,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6796,22 +6812,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6836,12 +6852,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6866,7 +6882,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6874,8 +6890,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>1</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6884,37 +6902,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6939,33 +6959,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6982,12 +7002,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7059,12 +7079,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7089,33 +7109,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7132,12 +7152,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7209,12 +7229,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7239,55 +7259,59 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7359,12 +7383,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7389,55 +7413,59 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7462,7 +7490,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7470,10 +7498,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7482,39 +7508,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7539,33 +7563,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7582,12 +7606,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7612,7 +7636,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7620,51 +7644,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7689,33 +7709,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>▲ 67,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7732,12 +7752,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7762,7 +7782,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7770,51 +7790,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7839,33 +7855,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7882,12 +7898,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7912,7 +7928,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7920,51 +7936,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7989,7 +8001,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7998,7 +8010,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8007,15 +8019,15 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8032,82 +8044,1866 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 1300,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,10 +1120,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1132,39 +1130,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,24 +1194,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1225,19 +1221,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1258,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,51 +1266,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,11 +1340,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1375,19 +1367,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,10 +1412,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1432,39 +1422,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1492,17 +1480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1525,19 +1513,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1570,51 +1558,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,16 +1632,16 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1665,7 +1649,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,19 +1659,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1712,7 +1696,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,10 +1704,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1732,39 +1714,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1825,19 +1805,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1948,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1975,19 +1955,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2039,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2098,11 +2078,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2125,19 +2105,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2162,7 +2142,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2170,8 +2150,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2180,37 +2162,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2235,7 +2219,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2243,51 +2227,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,7 +2292,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2320,8 +2300,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2330,37 +2312,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2388,17 +2372,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2421,19 +2405,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2469,9 +2453,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2494,19 +2478,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2531,33 +2515,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2567,19 +2551,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2613,11 +2597,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2640,19 +2624,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2690,7 +2674,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2703,7 +2687,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2713,19 +2697,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2759,7 +2743,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2786,19 +2770,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2832,11 +2816,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2859,19 +2843,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2927,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2973,7 +2957,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2981,51 +2965,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3086,19 +3066,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3123,20 +3103,20 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3145,11 +3125,11 @@
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3159,19 +3139,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3207,9 +3187,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3232,19 +3212,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3269,7 +3249,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3277,51 +3257,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 140,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3355,11 +3331,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3382,19 +3358,19 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3419,7 +3395,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3428,11 +3404,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3441,11 +3417,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3455,19 +3431,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3492,7 +3468,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3500,8 +3476,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>1</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3510,37 +3488,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3568,17 +3548,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3601,19 +3581,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3638,7 +3618,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3646,8 +3626,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3656,37 +3638,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3720,16 +3704,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3747,19 +3731,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3784,7 +3768,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3792,8 +3776,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3802,37 +3788,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3857,7 +3845,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,51 +3853,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3934,7 +3918,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3942,8 +3926,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3952,37 +3938,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4007,7 +3995,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4015,51 +4003,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I48" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4084,7 +4068,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4092,47 +4076,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4166,7 +4154,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4193,19 +4181,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4230,7 +4218,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4238,8 +4226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>1</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4248,37 +4238,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4314,9 +4306,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4346,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4423,12 +4415,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4462,11 +4454,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4496,12 +4488,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4526,7 +4518,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4534,8 +4526,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4544,37 +4538,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4602,17 +4598,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4642,12 +4638,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4672,7 +4668,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4680,47 +4676,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4788,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4826,8 +4826,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4836,37 +4838,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4902,7 +4906,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4934,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4964,7 +4968,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4972,47 +4976,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5050,7 +5058,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5080,12 +5088,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5110,7 +5118,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5118,8 +5126,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5128,37 +5138,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5192,7 +5204,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5226,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5267,9 +5279,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5299,12 +5311,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5376,12 +5388,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5415,7 +5427,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5449,12 +5461,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5522,12 +5534,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5563,9 +5575,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5595,12 +5607,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5628,7 +5640,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5636,7 +5648,7 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5661,19 +5673,19 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5701,17 +5713,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5734,19 +5746,19 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5780,7 +5792,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5801,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5797,7 +5809,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5807,19 +5819,19 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5844,7 +5856,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5853,7 +5865,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5862,15 +5874,15 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5880,19 +5892,19 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5920,9 +5932,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -5953,19 +5965,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6037,12 +6049,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6067,7 +6079,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6075,8 +6087,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6085,37 +6099,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6140,7 +6156,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6148,10 +6164,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6160,39 +6174,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6217,7 +6229,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6239,11 +6251,11 @@
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6253,19 +6265,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6290,7 +6302,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6298,10 +6310,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6310,39 +6320,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6414,12 +6422,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6455,9 +6463,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6480,19 +6488,19 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6517,7 +6525,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6539,11 +6547,11 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6553,19 +6561,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6599,11 +6607,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6626,19 +6634,19 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6666,7 +6674,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6674,7 +6682,7 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -6699,19 +6707,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6745,7 +6753,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6772,19 +6780,19 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6818,7 +6826,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6827,7 +6835,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6835,7 +6843,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6845,19 +6853,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6882,7 +6890,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6890,10 +6898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6902,39 +6908,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6959,7 +6963,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6967,47 +6971,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7032,7 +7040,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7040,10 +7048,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7052,39 +7058,37 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7109,7 +7113,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7117,8 +7121,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>1</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7127,37 +7133,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7182,7 +7190,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7190,51 +7198,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7259,7 +7263,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7267,10 +7271,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7279,39 +7281,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7344,10 +7344,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7356,39 +7354,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7413,7 +7409,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7421,51 +7417,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7490,7 +7482,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7498,8 +7490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7508,37 +7502,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7572,7 +7568,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7599,19 +7595,19 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7647,9 +7643,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7672,19 +7668,19 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7712,7 +7708,7 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7720,7 +7716,7 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7745,19 +7741,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7791,11 +7787,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7818,19 +7814,19 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7855,16 +7851,16 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7873,15 +7869,15 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7891,19 +7887,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7937,11 +7933,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7964,19 +7960,19 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8001,7 +7997,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8012,9 +8008,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8023,11 +8019,11 @@
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8037,19 +8033,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8083,11 +8079,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8110,19 +8106,19 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8156,7 +8152,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8183,19 +8179,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8220,7 +8216,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8228,10 +8224,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8240,39 +8234,37 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8333,19 +8325,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8381,9 +8373,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8401,24 +8393,24 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8443,16 +8435,18 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8461,37 +8455,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8525,11 +8521,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8552,19 +8548,19 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8589,20 +8585,20 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8611,11 +8607,11 @@
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8625,19 +8621,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8671,7 +8667,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8698,19 +8694,19 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8735,33 +8731,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8778,12 +8774,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8808,59 +8804,55 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8885,25 +8877,25 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
@@ -8911,7 +8903,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8928,12 +8920,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8958,7 +8950,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8966,10 +8958,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8978,39 +8968,37 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9035,33 +9023,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9078,12 +9066,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9155,12 +9143,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9185,33 +9173,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9228,12 +9216,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9305,12 +9293,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9335,33 +9323,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9378,12 +9366,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9455,12 +9443,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9485,55 +9473,59 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9558,7 +9550,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9566,10 +9558,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9578,39 +9568,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9635,33 +9623,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9678,12 +9666,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9708,7 +9696,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9716,51 +9704,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9785,33 +9769,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9828,82 +9812,3204 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -739,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -748,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -892,17 +888,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1039,33 +1035,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1112,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,8 +1116,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1130,39 +1128,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1228,14 +1228,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1269,9 +1269,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1340,24 +1340,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1480,17 +1480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1623,33 +1623,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1778,24 +1778,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,10 +1850,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1862,41 +1860,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1928,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2039,14 +2035,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2078,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2112,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2189,14 +2185,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2228,11 +2224,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2262,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2339,14 +2335,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2372,17 +2368,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2412,14 +2408,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2442,7 +2438,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2450,8 +2446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2460,39 +2458,41 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2515,33 +2515,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2631,14 +2631,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2666,20 +2666,20 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2777,14 +2777,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2818,22 +2818,22 @@
       <c r="I32" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2888,10 +2888,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2900,41 +2898,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2966,11 +2962,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3000,14 +2996,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3030,7 +3026,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3038,8 +3034,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3048,39 +3046,41 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3106,17 +3106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3146,14 +3146,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3187,9 +3187,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3219,14 +3219,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3249,33 +3249,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 140,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3331,11 +3331,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3365,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3404,24 +3404,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>24</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 140,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3476,10 +3476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3488,41 +3486,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3548,17 +3544,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3588,12 +3584,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3665,14 +3661,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3695,33 +3691,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3738,12 +3734,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3815,14 +3811,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3845,7 +3841,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3854,24 +3850,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3888,12 +3884,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3965,14 +3961,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4004,11 +4000,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1300,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4038,12 +4034,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4115,14 +4111,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4154,11 +4150,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4188,12 +4184,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4265,14 +4261,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4304,7 +4300,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4331,19 +4327,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4415,14 +4411,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4456,9 +4452,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4488,12 +4484,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4565,14 +4561,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4598,17 +4594,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4638,12 +4634,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4715,14 +4711,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4745,33 +4741,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4788,12 +4784,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4865,14 +4861,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4895,7 +4891,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4904,24 +4900,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4938,12 +4934,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5015,14 +5011,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5054,11 +5050,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5088,12 +5084,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,12 +5161,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5208,7 +5204,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5238,14 +5234,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5268,7 +5264,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5276,8 +5272,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5286,39 +5284,41 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5349,10 +5349,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5361,39 +5359,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5461,14 +5457,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5491,7 +5487,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5499,8 +5495,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5509,39 +5507,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5575,9 +5575,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5640,17 +5640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5680,14 +5680,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5719,11 +5719,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5783,33 +5783,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5899,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5947,15 +5947,15 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5972,14 +5972,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6010,10 +6010,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6022,41 +6020,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6079,7 +6075,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6087,10 +6083,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6099,41 +6093,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6156,7 +6148,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6164,8 +6156,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6174,39 +6168,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6229,7 +6225,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6237,8 +6233,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6247,37 +6245,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6345,14 +6345,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6383,10 +6383,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6395,41 +6393,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6463,9 +6459,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6495,14 +6491,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6525,7 +6521,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6533,8 +6529,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6543,39 +6541,41 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6641,14 +6641,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6671,20 +6671,20 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6693,11 +6693,11 @@
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6714,14 +6714,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6787,14 +6787,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6817,33 +6817,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6860,12 +6860,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6933,14 +6933,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6971,10 +6971,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6983,39 +6981,37 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7083,12 +7079,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7160,14 +7156,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7201,9 +7197,9 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7233,14 +7229,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7263,7 +7259,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7271,8 +7267,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7281,39 +7279,41 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7345,11 +7345,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7379,14 +7379,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7420,9 +7420,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7452,14 +7452,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7490,10 +7490,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7502,41 +7500,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7568,11 +7564,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7602,14 +7598,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7632,7 +7628,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7640,8 +7636,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7650,39 +7648,41 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7708,17 +7708,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7748,14 +7748,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7789,9 +7789,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7821,14 +7821,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7851,33 +7851,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7894,14 +7894,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7933,11 +7933,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8006,24 +8006,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8040,14 +8040,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8079,11 +8079,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8113,14 +8113,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8152,11 +8152,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8186,14 +8186,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8225,11 +8225,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8259,14 +8259,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8332,14 +8332,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8371,11 +8371,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8405,14 +8405,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8443,10 +8443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8455,41 +8453,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8521,11 +8517,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8555,14 +8551,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8585,7 +8581,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8593,8 +8589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8603,39 +8601,41 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8701,14 +8701,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8734,17 +8734,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8767,21 +8767,21 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8807,17 +8807,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8840,21 +8840,21 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8877,33 +8877,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8920,14 +8920,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8950,33 +8950,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8993,14 +8993,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9023,16 +9023,16 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9041,15 +9041,15 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9066,14 +9066,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9104,10 +9104,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9116,41 +9114,39 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9173,12 +9169,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -9195,11 +9191,11 @@
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9216,12 +9212,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9293,14 +9289,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9323,7 +9319,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9345,11 +9341,11 @@
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9366,12 +9362,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9443,14 +9439,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9473,7 +9469,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9481,10 +9477,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9493,41 +9487,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9550,7 +9542,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9558,8 +9550,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9568,39 +9562,41 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9623,7 +9619,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9631,8 +9627,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9641,39 +9639,41 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9707,9 +9707,9 @@
       <c r="I125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9739,14 +9739,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9772,17 +9772,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9812,14 +9812,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9851,11 +9851,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9885,14 +9885,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9915,33 +9915,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9958,14 +9958,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9996,10 +9996,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10008,41 +10006,39 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10065,7 +10061,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10074,24 +10070,24 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10108,12 +10104,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10185,14 +10181,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10224,11 +10220,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10258,12 +10254,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10335,14 +10331,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10365,7 +10361,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10373,10 +10369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10385,39 +10379,37 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10489,12 +10481,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10566,14 +10558,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10596,7 +10588,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10604,8 +10596,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10614,39 +10608,41 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10669,7 +10665,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10677,8 +10673,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10687,39 +10685,41 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10753,9 +10753,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10785,14 +10785,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10818,17 +10818,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10858,14 +10858,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10897,11 +10897,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10931,14 +10931,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10961,33 +10961,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11004,14 +11004,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11043,11 +11043,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11077,14 +11077,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11107,16 +11107,16 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11125,15 +11125,15 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11150,14 +11150,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11189,11 +11189,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11223,14 +11223,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11275,11 +11275,11 @@
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11296,14 +11296,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11334,10 +11334,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11346,39 +11344,37 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11446,14 +11442,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11476,7 +11472,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11484,8 +11480,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11494,39 +11492,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11552,9 +11552,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
@@ -11592,14 +11592,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11633,9 +11633,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11665,14 +11665,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11695,20 +11695,20 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11717,11 +11717,11 @@
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11738,14 +11738,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11777,11 +11777,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11811,14 +11811,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11841,33 +11841,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11884,14 +11884,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -11922,10 +11922,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11934,41 +11932,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11991,33 +11987,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12034,12 +12030,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12111,14 +12107,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12141,33 +12137,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12184,12 +12180,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12261,14 +12257,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12291,33 +12287,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12334,12 +12330,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12411,14 +12407,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12441,33 +12437,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12484,12 +12480,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12561,14 +12557,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12591,33 +12587,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12634,12 +12630,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12711,14 +12707,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12741,33 +12737,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12784,12 +12780,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12861,14 +12857,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12891,33 +12887,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12934,82 +12930,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,41 +826,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -894,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1038,17 +1034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1185,33 +1181,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1258,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,8 +1262,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1276,39 +1274,41 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1336,20 +1336,20 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1415,9 +1415,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1486,24 +1486,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1626,17 +1626,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1769,33 +1769,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,24 +1924,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,10 +1996,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2008,41 +2006,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2074,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2185,14 +2181,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2224,11 +2220,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2258,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2335,14 +2331,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2374,11 +2370,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2408,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2485,14 +2481,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2518,17 +2514,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2558,14 +2554,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2596,8 +2592,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2606,39 +2604,41 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2661,33 +2661,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2777,14 +2777,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2812,20 +2812,20 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2923,14 +2923,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2964,22 +2964,22 @@
       <c r="I34" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2996,14 +2996,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3034,10 +3034,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3046,41 +3044,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3112,11 +3108,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3146,14 +3142,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3176,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3184,8 +3180,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3194,39 +3192,41 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3252,17 +3252,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3333,9 +3333,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3365,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3395,33 +3395,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 140,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3477,11 +3477,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3511,14 +3511,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3550,24 +3550,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>24</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 140,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3622,10 +3622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3634,41 +3632,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3694,17 +3690,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3734,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3811,14 +3807,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3841,33 +3837,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3884,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3961,14 +3957,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3991,7 +3987,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4000,24 +3996,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4034,12 +4030,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4111,14 +4107,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4150,11 +4146,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1300,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4184,12 +4180,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,14 +4257,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4300,11 +4296,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4334,12 +4330,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4411,14 +4407,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4450,7 +4446,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4477,19 +4473,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4561,14 +4557,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4602,9 +4598,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4634,12 +4630,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4711,14 +4707,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4744,17 +4740,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4784,12 +4780,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4861,14 +4857,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4891,33 +4887,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4934,12 +4930,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5011,14 +5007,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5041,7 +5037,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5050,24 +5046,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5084,12 +5080,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5161,14 +5157,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5200,11 +5196,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5234,12 +5230,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5311,12 +5307,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5354,7 +5350,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5384,14 +5380,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5414,7 +5410,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5422,8 +5418,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5432,39 +5430,41 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5495,10 +5495,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5507,39 +5505,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5607,14 +5603,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5637,7 +5633,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5645,8 +5641,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5655,39 +5653,41 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5721,9 +5721,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5786,17 +5786,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,14 +5826,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5865,11 +5865,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5899,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5929,33 +5929,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6045,14 +6045,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6093,15 +6093,15 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6118,14 +6118,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6156,10 +6156,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6168,41 +6166,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6233,10 +6229,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6245,41 +6239,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6302,7 +6294,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6310,8 +6302,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6320,39 +6314,41 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6375,7 +6371,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6383,8 +6379,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6393,37 +6391,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6491,14 +6491,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6529,10 +6529,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6541,41 +6539,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6609,9 +6605,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6641,14 +6637,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6671,7 +6667,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6679,8 +6675,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6689,39 +6687,41 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6787,14 +6787,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6817,20 +6817,20 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6839,11 +6839,11 @@
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6860,14 +6860,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6933,14 +6933,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6963,33 +6963,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7006,12 +7006,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7079,14 +7079,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7117,10 +7117,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7129,39 +7127,37 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7229,12 +7225,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7306,14 +7302,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7347,9 +7343,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7379,14 +7375,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7409,7 +7405,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7417,8 +7413,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7427,39 +7425,41 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7491,11 +7491,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7525,14 +7525,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7566,9 +7566,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7598,14 +7598,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7636,10 +7636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7648,41 +7646,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7714,11 +7710,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7748,14 +7744,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7778,7 +7774,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7786,8 +7782,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7796,39 +7794,41 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7854,17 +7854,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7894,14 +7894,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7935,9 +7935,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7997,33 +7997,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8040,14 +8040,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8079,11 +8079,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8113,14 +8113,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8152,24 +8152,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8186,14 +8186,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8225,11 +8225,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8259,14 +8259,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8298,11 +8298,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8332,14 +8332,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8371,11 +8371,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8405,14 +8405,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8478,14 +8478,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8517,11 +8517,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8551,14 +8551,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8589,10 +8589,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8601,41 +8599,39 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8667,11 +8663,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8701,14 +8697,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8731,7 +8727,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8739,8 +8735,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8749,39 +8747,41 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8847,14 +8847,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8880,17 +8880,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8913,21 +8913,21 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8953,17 +8953,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8986,21 +8986,21 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9023,33 +9023,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9066,14 +9066,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9096,33 +9096,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9139,14 +9139,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9169,16 +9169,16 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9187,15 +9187,15 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9212,14 +9212,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9250,10 +9250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9262,41 +9260,39 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9319,12 +9315,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -9341,11 +9337,11 @@
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9362,12 +9358,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9439,14 +9435,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9469,7 +9465,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9491,11 +9487,11 @@
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9512,12 +9508,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9589,14 +9585,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9619,7 +9615,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9627,10 +9623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9639,41 +9633,39 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9696,7 +9688,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9704,8 +9696,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9714,39 +9708,41 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9769,7 +9765,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9777,8 +9773,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9787,39 +9785,41 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9853,9 +9853,9 @@
       <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9885,14 +9885,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9918,17 +9918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9958,14 +9958,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9997,11 +9997,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10031,14 +10031,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10061,33 +10061,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10104,14 +10104,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10142,10 +10142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10154,41 +10152,39 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10211,7 +10207,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10220,24 +10216,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10254,12 +10250,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10331,14 +10327,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10370,11 +10366,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10404,12 +10400,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10481,14 +10477,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10511,7 +10507,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10519,10 +10515,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I136" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10531,39 +10525,37 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10635,12 +10627,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10712,14 +10704,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10742,7 +10734,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10750,8 +10742,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10760,39 +10754,41 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10815,7 +10811,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10823,8 +10819,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -10833,39 +10831,41 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10899,9 +10899,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10931,14 +10931,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10964,17 +10964,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11004,14 +11004,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11043,11 +11043,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11077,14 +11077,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11107,33 +11107,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11150,14 +11150,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11189,11 +11189,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11223,14 +11223,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11253,16 +11253,16 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11271,15 +11271,15 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11296,14 +11296,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11335,11 +11335,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11369,14 +11369,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11442,14 +11442,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11480,10 +11480,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11492,39 +11490,37 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11592,14 +11588,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11622,7 +11618,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11630,8 +11626,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11640,39 +11638,41 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11698,9 +11698,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
@@ -11738,14 +11738,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11779,9 +11779,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11811,14 +11811,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11841,20 +11841,20 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11863,11 +11863,11 @@
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11884,14 +11884,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11923,11 +11923,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11957,14 +11957,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11987,33 +11987,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12030,14 +12030,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12068,10 +12068,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12080,41 +12078,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12137,33 +12133,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12180,12 +12176,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12257,14 +12253,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12287,33 +12283,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12330,12 +12326,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12407,14 +12403,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12437,33 +12433,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12480,12 +12476,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12557,14 +12553,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12587,33 +12583,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12630,12 +12626,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12707,14 +12703,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12737,33 +12733,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12780,12 +12776,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12857,14 +12853,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12887,33 +12883,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12930,12 +12926,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13007,14 +13003,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -13037,33 +13033,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13080,82 +13076,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -974,41 +972,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1031,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1040,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 77,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1184,17 +1180,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1331,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,14 +1370,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1404,7 +1400,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,8 +1408,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1422,39 +1420,41 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1482,20 +1482,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1561,9 +1561,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1772,17 +1772,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1915,33 +1915,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2070,24 +2070,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2142,10 +2142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2154,41 +2152,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2220,11 +2216,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2331,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2370,11 +2366,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2404,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2481,14 +2477,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2520,11 +2516,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2554,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2631,14 +2627,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2664,17 +2660,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 37,5%</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2704,14 +2700,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2734,7 +2730,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2742,8 +2738,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2752,39 +2750,41 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2807,33 +2807,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2923,14 +2923,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2996,12 +2996,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,14 +3069,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3110,22 +3110,22 @@
       <c r="I36" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3142,14 +3142,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3180,10 +3180,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3192,41 +3190,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3258,11 +3254,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3292,14 +3288,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3322,7 +3318,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3330,8 +3326,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3340,39 +3338,41 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3398,17 +3398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3479,9 +3479,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3511,14 +3511,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3541,33 +3541,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 140,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3623,11 +3623,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3657,14 +3657,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3696,24 +3696,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>24</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 140,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3730,14 +3730,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3768,10 +3768,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3780,41 +3778,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3840,17 +3836,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3880,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3957,14 +3953,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -3987,33 +3983,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4030,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4107,14 +4103,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4137,7 +4133,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4146,24 +4142,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4180,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4257,14 +4253,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4296,11 +4292,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1300,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4330,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4407,14 +4403,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4446,11 +4442,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4480,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4557,14 +4553,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4596,7 +4592,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4623,19 +4619,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4707,14 +4703,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4748,9 +4744,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4780,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4857,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -4890,17 +4886,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4930,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5007,14 +5003,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5037,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5080,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5157,14 +5153,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5187,7 +5183,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5196,24 +5192,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5230,12 +5226,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5307,14 +5303,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5346,11 +5342,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5380,12 +5376,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5457,12 +5453,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5500,7 +5496,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5530,14 +5526,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5560,7 +5556,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5568,8 +5564,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5578,39 +5576,41 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5641,10 +5641,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5653,39 +5651,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,14 +5749,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5783,7 +5779,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5791,8 +5787,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5801,39 +5799,41 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5867,9 +5867,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5899,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -5932,17 +5932,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5972,14 +5972,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6011,11 +6011,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6045,14 +6045,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6075,33 +6075,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6191,14 +6191,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6239,15 +6239,15 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6264,14 +6264,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6302,10 +6302,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6314,41 +6312,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6371,7 +6367,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6379,10 +6375,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6391,41 +6385,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6448,7 +6440,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6456,8 +6448,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6466,39 +6460,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6521,7 +6517,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6529,8 +6525,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6539,37 +6537,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6637,14 +6637,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6675,10 +6675,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6687,41 +6685,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6755,9 +6751,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6787,14 +6783,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6817,7 +6813,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6825,8 +6821,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6835,39 +6833,41 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6899,11 +6899,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6933,14 +6933,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -6963,20 +6963,20 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6985,11 +6985,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7006,14 +7006,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7079,14 +7079,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7109,33 +7109,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7225,14 +7225,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7263,10 +7263,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7275,39 +7273,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7375,12 +7371,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7452,14 +7448,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7493,9 +7489,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7525,14 +7521,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7555,7 +7551,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7563,8 +7559,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7573,39 +7571,41 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7637,11 +7637,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7671,14 +7671,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7712,9 +7712,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7744,14 +7744,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7782,10 +7782,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7794,41 +7792,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7860,11 +7856,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7894,14 +7890,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -7924,7 +7920,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7932,8 +7928,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7942,39 +7940,41 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8000,17 +8000,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8040,14 +8040,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8081,9 +8081,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8113,14 +8113,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8143,33 +8143,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8186,14 +8186,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8225,11 +8225,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8259,14 +8259,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8298,24 +8298,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8332,14 +8332,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8371,11 +8371,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8405,14 +8405,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8444,11 +8444,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8478,14 +8478,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8517,11 +8517,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8551,14 +8551,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8624,14 +8624,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8663,11 +8663,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8697,14 +8697,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8735,10 +8735,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8747,41 +8745,39 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8813,11 +8809,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8847,14 +8843,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8877,7 +8873,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8885,8 +8881,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8895,39 +8893,41 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8993,14 +8993,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9026,17 +9026,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9059,21 +9059,21 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9099,17 +9099,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9132,21 +9132,21 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9169,33 +9169,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9212,14 +9212,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9242,33 +9242,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9285,14 +9285,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9315,16 +9315,16 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9333,15 +9333,15 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9358,14 +9358,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9396,10 +9396,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9408,41 +9406,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9465,12 +9461,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -9487,11 +9483,11 @@
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9508,12 +9504,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9585,14 +9581,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9615,7 +9611,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9637,11 +9633,11 @@
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9658,12 +9654,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9735,14 +9731,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9765,7 +9761,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9773,10 +9769,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9785,41 +9779,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9842,7 +9834,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9850,8 +9842,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9860,39 +9854,41 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9915,7 +9911,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9923,8 +9919,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="n">
-        <v>0</v>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -9933,39 +9931,41 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -9999,9 +9999,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10031,14 +10031,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10064,17 +10064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10104,14 +10104,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10143,11 +10143,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10177,14 +10177,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10207,33 +10207,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10250,14 +10250,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10288,10 +10288,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10300,41 +10298,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10357,7 +10353,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10366,24 +10362,24 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10400,12 +10396,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10477,14 +10473,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10516,11 +10512,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10550,12 +10546,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10627,14 +10623,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10657,7 +10653,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10665,10 +10661,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10677,39 +10671,37 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10781,12 +10773,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10858,14 +10850,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10888,7 +10880,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10896,8 +10888,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -10906,39 +10900,41 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -10961,7 +10957,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -10969,8 +10965,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>0</v>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -10979,39 +10977,41 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11045,9 +11045,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11077,14 +11077,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11110,17 +11110,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11150,14 +11150,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11189,11 +11189,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11223,14 +11223,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11253,33 +11253,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11296,14 +11296,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11335,11 +11335,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11369,14 +11369,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11399,16 +11399,16 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11417,15 +11417,15 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11442,14 +11442,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11481,11 +11481,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11515,14 +11515,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11567,11 +11567,11 @@
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11588,14 +11588,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11626,10 +11626,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11638,39 +11636,37 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11738,14 +11734,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11768,7 +11764,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11776,8 +11772,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11786,39 +11784,41 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11844,9 +11844,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
@@ -11884,14 +11884,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11925,9 +11925,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11957,14 +11957,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -11987,20 +11987,20 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12009,11 +12009,11 @@
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12030,14 +12030,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12069,11 +12069,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12103,14 +12103,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12133,33 +12133,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12176,14 +12176,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12214,10 +12214,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12226,41 +12224,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12283,33 +12279,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12326,12 +12322,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12403,14 +12399,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12433,33 +12429,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>26</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12476,12 +12472,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12553,14 +12549,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12583,33 +12579,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,7%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 4,2%</t>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12626,12 +12622,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12703,14 +12699,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12733,33 +12729,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,2%</t>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12776,12 +12772,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12853,14 +12849,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -12883,33 +12879,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>24</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12926,12 +12922,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13003,14 +12999,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -13033,33 +13029,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>▲ 48,5%</t>
+          <t>▲ 67,3%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,3%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13076,12 +13072,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13153,14 +13149,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-095-CZ</t>
@@ -13183,33 +13179,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13226,82 +13222,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
+++ b/saida_skus/SKU_UTD-095-CZ-SECA-SALADAS-CINZA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +748,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +823,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +967,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1040,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,10 +1112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1120,39 +1122,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 77,8%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1258,10 +1258,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1270,39 +1268,37 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,12 +1323,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1340,20 +1336,20 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1396,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,51 +1404,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>18</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1559,7 +1551,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1593,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,47 +1696,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1782,7 +1778,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 77,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,7 +1838,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,8 +1846,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1860,37 +1858,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1924,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,47 +1996,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,25 +2065,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2104,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2143,7 +2147,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2177,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2216,24 +2220,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2288,51 +2292,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2438,10 +2438,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2450,39 +2448,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2510,17 +2506,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2550,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2580,7 +2576,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2588,51 +2584,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2657,7 +2649,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2666,24 +2658,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2700,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2738,10 +2730,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2750,39 +2740,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2810,17 +2798,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 37,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2850,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2880,7 +2868,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2888,8 +2876,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2898,37 +2888,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2953,33 +2945,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2996,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3026,7 +3018,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3034,8 +3026,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3044,37 +3038,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3099,7 +3095,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3108,24 +3104,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3142,12 +3138,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3172,7 +3168,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3180,8 +3176,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3190,37 +3188,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3254,11 +3254,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▲ 37,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3541,33 +3541,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 70,8%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3625,9 +3625,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3696,24 +3696,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 140,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3803,12 +3803,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3842,11 +3842,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3876,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3986,17 +3986,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4064,10 +4064,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4076,39 +4074,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4133,33 +4129,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,8%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4176,12 +4172,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4206,7 +4202,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4214,51 +4210,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4283,7 +4275,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4292,24 +4284,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>24</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 140,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4326,12 +4318,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4356,7 +4348,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4364,10 +4356,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4376,39 +4366,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4442,11 +4430,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1300,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4476,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,12 +4541,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4586,17 +4574,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4626,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4733,7 +4721,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4742,24 +4730,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4769,19 +4757,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,12 +4841,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4892,11 +4880,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4919,19 +4907,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5003,12 +4991,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5036,17 +5024,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>14</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1300,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5069,19 +5057,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5183,7 +5171,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5192,7 +5180,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5201,15 +5189,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5219,19 +5207,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5303,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5344,9 +5332,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5376,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5453,12 +5441,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5492,11 +5480,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5526,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,12 +5591,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5636,17 +5624,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5676,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5706,7 +5694,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5714,8 +5702,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5724,37 +5714,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5779,7 +5771,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5787,10 +5779,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5799,39 +5789,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5856,7 +5844,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5864,8 +5852,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5874,37 +5864,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5940,9 +5932,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5972,12 +5964,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6002,7 +5994,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6010,47 +6002,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6078,17 +6074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6118,12 +6114,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6148,7 +6144,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6156,47 +6152,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6239,15 +6239,15 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6264,12 +6264,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6375,8 +6375,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6385,37 +6387,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6440,7 +6444,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6448,10 +6452,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6460,39 +6462,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6525,10 +6525,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6537,39 +6535,37 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6605,9 +6601,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6637,12 +6633,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6667,20 +6663,20 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6689,11 +6685,11 @@
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6710,12 +6706,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6749,11 +6745,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6783,12 +6779,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6813,7 +6809,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6821,10 +6817,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6833,39 +6827,37 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6899,11 +6891,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6933,12 +6925,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6963,7 +6955,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6985,11 +6977,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7006,12 +6998,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7036,7 +7028,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7044,8 +7036,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>1</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7054,37 +7048,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7109,55 +7105,59 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7225,12 +7225,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7298,12 +7298,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7489,9 +7489,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7559,10 +7559,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7571,39 +7569,37 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7637,11 +7633,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7671,12 +7667,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7704,17 +7700,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7744,12 +7740,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7783,7 +7779,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7817,12 +7813,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7847,7 +7843,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7856,24 +7852,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7890,12 +7886,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7920,7 +7916,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7928,10 +7924,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7940,39 +7934,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7997,7 +7989,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8005,8 +7997,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>1</v>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8015,37 +8009,39 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8113,12 +8109,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8143,55 +8139,59 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8307,15 +8307,15 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8332,12 +8332,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8516,47 +8516,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8624,12 +8628,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8663,7 +8667,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8697,12 +8701,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8730,17 +8734,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8770,12 +8774,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8843,12 +8847,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8873,7 +8877,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8881,10 +8885,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8893,39 +8895,37 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9034,9 +9034,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9107,9 +9107,9 @@
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9172,17 +9172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9205,19 +9205,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9245,17 +9245,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9278,19 +9278,19 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9333,15 +9333,15 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9351,19 +9351,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9397,24 +9397,24 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9461,16 +9461,18 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9479,37 +9481,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9534,7 +9538,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9542,10 +9546,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9554,39 +9556,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9633,11 +9633,11 @@
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9647,19 +9647,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9692,10 +9692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9704,39 +9702,37 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9764,17 +9760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9804,12 +9800,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9834,59 +9830,55 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9911,7 +9903,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9919,10 +9911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -9931,39 +9921,37 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9988,7 +9976,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9997,7 +9985,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10006,15 +9994,15 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -10031,12 +10019,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10064,9 +10052,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -10104,12 +10092,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10134,7 +10122,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10142,47 +10130,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10207,20 +10199,20 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10229,11 +10221,11 @@
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10250,12 +10242,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10280,7 +10272,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10288,8 +10280,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
-        <v>1</v>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10298,37 +10292,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10353,7 +10349,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10362,7 +10358,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10371,15 +10367,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10396,12 +10392,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10473,12 +10469,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10503,7 +10499,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10511,47 +10507,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10584,10 +10584,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10596,39 +10594,37 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10662,7 +10658,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10696,12 +10692,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10726,7 +10722,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10734,51 +10730,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10803,59 +10795,55 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10880,7 +10868,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10888,10 +10876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -10900,39 +10886,37 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10957,7 +10941,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -10965,10 +10949,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I142" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -10977,39 +10959,37 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11034,7 +11014,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11042,8 +11022,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11052,37 +11034,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11118,9 +11102,9 @@
       <c r="I144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11150,12 +11134,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11180,7 +11164,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11188,47 +11172,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11256,17 +11244,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11296,12 +11284,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11326,7 +11314,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11334,47 +11322,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11399,16 +11391,18 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>21</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11417,37 +11411,39 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11472,7 +11468,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11480,47 +11476,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11553,8 +11553,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="2" t="n">
-        <v>0</v>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -11563,37 +11565,39 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11627,7 +11631,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11661,12 +11665,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11734,12 +11738,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11764,7 +11768,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11772,51 +11776,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11844,17 +11844,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11884,12 +11884,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11923,11 +11923,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11957,12 +11957,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11987,16 +11987,16 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12005,15 +12005,15 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12069,11 +12069,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12103,12 +12103,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12136,17 +12136,17 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,1%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12249,12 +12249,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12279,33 +12279,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 96,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12399,12 +12399,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12429,33 +12429,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12472,12 +12472,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12510,10 +12510,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12522,39 +12520,37 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12579,33 +12575,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 48,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12622,12 +12618,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12652,7 +12648,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12660,51 +12656,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12729,33 +12721,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,7%</t>
+          <t>▼ 47,1%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 4,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12772,12 +12764,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12802,7 +12794,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12810,10 +12802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12822,39 +12812,37 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12879,33 +12867,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 101,00</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,2%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 96,2%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12922,12 +12910,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12999,12 +12987,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13029,33 +13017,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,3%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,5%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13072,12 +13060,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13149,12 +13137,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13188,16 +13176,16 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,3%</t>
+        <v>28</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
@@ -13205,7 +13193,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13222,12 +13210,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13299,12 +13287,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13332,22 +13320,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,7%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
@@ -13355,7 +13343,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13372,82 +13360,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,2%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,3%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 48,5%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,3%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4851144626</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-CZ</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Seca saladas cinza</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3771471049</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-CZ</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Seca saladas cinza</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4851144626</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>